--- a/v2/transformer_design_tool_v2.xlsx
+++ b/v2/transformer_design_tool_v2.xlsx
@@ -854,7 +854,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>D_max（Vin_min 处）</t>
+          <t>D_design 设计占空比上限（工程默认值，可改）</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
@@ -862,7 +862,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>反激=开关；正激=单管；桥式=每管</t>
+          <t>反激 0.60 / 正激 0.45（电容复位 0.60）/ 推挽·桥式 0.45 / LLC 0.50；超出只提示确认</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D156"/>
+  <dimension ref="A1:D157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2606,7 +2606,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>D_max（Vin_min 处）</t>
+          <t>D_design 设计占空比上限（工程默认值，可改）</t>
         </is>
       </c>
       <c r="B16" s="9">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>反激=开关；正激=单管；桥式=每管</t>
+          <t>反激 0.60 / 正激 0.45（电容复位 0.60）/ 推挽·桥式 0.45 / LLC 0.50；超出只提示确认</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -3420,14 +3420,18 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>拓扑占空比上限</t>
+          <t>拓扑/电路硬上限 D_topo</t>
         </is>
       </c>
       <c r="B62" s="12">
-        <f>IF($B$52,0.6,IF($B$53,0.5,IF($B$57,0.5,0.48)))</f>
-        <v/>
-      </c>
-      <c r="C62" s="5" t="inlineStr"/>
+        <f>IF($B$52,0.95,IF($B$53,0.50,IF($B$57,0.50,0.50)))</f>
+        <v/>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>反激无固定值（真正约束是 V_or/耐压与复位时间，0.95 = 不设限）；正激 0.50 = 1:1 复位绕组，电容复位需按复位电路算</t>
+        </is>
+      </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
           <t>B62</t>
@@ -3437,14 +3441,18 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>D_max（钳位后）</t>
-        </is>
-      </c>
-      <c r="B63" s="14">
-        <f>MIN($B$16,$B$62)</f>
-        <v/>
-      </c>
-      <c r="C63" s="5" t="inlineStr"/>
+          <t>控制器允许上限 D_controller</t>
+        </is>
+      </c>
+      <c r="B63" s="12">
+        <f>0.95</f>
+        <v/>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>按芯片手册改；推挽/桥式 = 0.5 − t_dead·Fs</t>
+        </is>
+      </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
           <t>B63</t>
@@ -3454,14 +3462,18 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Po (W)</t>
-        </is>
-      </c>
-      <c r="B64" s="12">
-        <f>$B$11*$B$12</f>
-        <v/>
-      </c>
-      <c r="C64" s="5" t="inlineStr"/>
+          <t>D_allowed = min(拓扑, 控制器, 设计)</t>
+        </is>
+      </c>
+      <c r="B64" s="14">
+        <f>MIN($B$16,$B$63,$B$62)</f>
+        <v/>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>设计裕量 D_design 超出只提示确认，不判物理失败</t>
+        </is>
+      </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
           <t>B64</t>
@@ -3471,11 +3483,11 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Pin (W)</t>
+          <t>Po (W)</t>
         </is>
       </c>
       <c r="B65" s="12">
-        <f>$B$64/$B$15</f>
+        <f>$B$11*$B$12</f>
         <v/>
       </c>
       <c r="C65" s="5" t="inlineStr"/>
@@ -3488,11 +3500,11 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Vo = Vout+Vf (V)</t>
+          <t>Pin (W)</t>
         </is>
       </c>
       <c r="B66" s="12">
-        <f>$B$11+$B$13</f>
+        <f>$B$65/$B$15</f>
         <v/>
       </c>
       <c r="C66" s="5" t="inlineStr"/>
@@ -3505,11 +3517,11 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Vin_nom（LLC 用）</t>
-        </is>
-      </c>
-      <c r="B67" s="11">
-        <f>IF($B$7&gt;0,$B$7,($B$9+$B$10)/2)</f>
+          <t>Vo = Vout+Vf (V)</t>
+        </is>
+      </c>
+      <c r="B67" s="12">
+        <f>$B$11+$B$13</f>
         <v/>
       </c>
       <c r="C67" s="5" t="inlineStr"/>
@@ -3522,11 +3534,11 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>目标变比 n=Np/Ns</t>
-        </is>
-      </c>
-      <c r="B68" s="14">
-        <f>IF($B$52,$B$9*$B$63/((1-$B$63)*$B$66),IF($B$53,$B$9*$B$63/$B$66,IF($B$58,$B$60*$B$9*$B$63/$B$66,$B$67/(2*$B$66))))</f>
+          <t>Vin_nom（LLC 用）</t>
+        </is>
+      </c>
+      <c r="B68" s="11">
+        <f>IF($B$7&gt;0,$B$7,($B$9+$B$10)/2)</f>
         <v/>
       </c>
       <c r="C68" s="5" t="inlineStr"/>
@@ -3539,11 +3551,11 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>D_max 点占空比(Vin_min,目标比)</t>
+          <t>目标变比 n=Np/Ns</t>
         </is>
       </c>
       <c r="B69" s="14">
-        <f>IF($B$52,$B$68*$B$66/($B$9+$B$68*$B$66),IF($B$53,$B$68*$B$66/$B$9,IF($B$58,$B$68*$B$66/($B$60*$B$9),0.5)))</f>
+        <f>IF($B$52,$B$9*$B$64/((1-$B$64)*$B$67),IF($B$53,$B$9*$B$64/$B$67,IF($B$58,$B$60*$B$9*$B$64/$B$67,$B$68/(2*$B$67))))</f>
         <v/>
       </c>
       <c r="C69" s="5" t="inlineStr"/>
@@ -3556,11 +3568,11 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>D@Vin_max(目标比)</t>
+          <t>D_max 点占空比(Vin_min,目标比)</t>
         </is>
       </c>
       <c r="B70" s="14">
-        <f>IF($B$52,$B$68*$B$66/($B$10+$B$68*$B$66),IF($B$53,$B$68*$B$66/$B$10,IF($B$58,$B$68*$B$66/($B$60*$B$10),0.5)))</f>
+        <f>IF($B$52,$B$69*$B$67/($B$9+$B$69*$B$67),IF($B$53,$B$69*$B$67/$B$9,IF($B$58,$B$69*$B$67/($B$60*$B$9),0.5)))</f>
         <v/>
       </c>
       <c r="C70" s="5" t="inlineStr"/>
@@ -3573,11 +3585,11 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>V·t@Vin_min (V·s)</t>
-        </is>
-      </c>
-      <c r="B71" s="15">
-        <f>$B$61*$B$9*$B$69/$B$41</f>
+          <t>D@Vin_max(目标比)</t>
+        </is>
+      </c>
+      <c r="B71" s="14">
+        <f>IF($B$52,$B$69*$B$67/($B$10+$B$69*$B$67),IF($B$53,$B$69*$B$67/$B$10,IF($B$58,$B$69*$B$67/($B$60*$B$10),0.5)))</f>
         <v/>
       </c>
       <c r="C71" s="5" t="inlineStr"/>
@@ -3590,11 +3602,11 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>V·t@Vin_max (V·s)</t>
+          <t>V·t@Vin_min (V·s)</t>
         </is>
       </c>
       <c r="B72" s="15">
-        <f>$B$61*$B$10*$B$70/$B$41</f>
+        <f>$B$61*$B$9*$B$70/$B$41</f>
         <v/>
       </c>
       <c r="C72" s="5" t="inlineStr"/>
@@ -3607,11 +3619,11 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>V·t 最恶劣 (V·s)</t>
+          <t>V·t@Vin_max (V·s)</t>
         </is>
       </c>
       <c r="B73" s="15">
-        <f>MAX($B$71,$B$72)</f>
+        <f>$B$61*$B$10*$B$71/$B$41</f>
         <v/>
       </c>
       <c r="C73" s="5" t="inlineStr"/>
@@ -3624,11 +3636,11 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>Ae (m²)</t>
+          <t>V·t 最恶劣 (V·s)</t>
         </is>
       </c>
       <c r="B74" s="15">
-        <f>$B$42/1000000</f>
+        <f>MAX($B$72,$B$73)</f>
         <v/>
       </c>
       <c r="C74" s="5" t="inlineStr"/>
@@ -3641,11 +3653,11 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>磁通决定 Np 下限</t>
-        </is>
-      </c>
-      <c r="B75" s="10">
-        <f>MAX(1,CEILING($B$73/($B$74*$B$17),1))</f>
+          <t>Ae (m²)</t>
+        </is>
+      </c>
+      <c r="B75" s="15">
+        <f>$B$42/1000000</f>
         <v/>
       </c>
       <c r="C75" s="5" t="inlineStr"/>
@@ -3658,11 +3670,11 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>原边峰值 Ipk (A)</t>
-        </is>
-      </c>
-      <c r="B76" s="16">
-        <f>IF($B$52,IF($B$19&gt;=2,2*$B$65/($B$9*$B$63),($B$65/$B$9/$B$63)/(1-$B$19/2)),IF($B$57,$B$65/(0.5*$B$67)*1.414,($B$12+$B$20/2)/$B$68))</f>
+          <t>磁通决定 Np 下限</t>
+        </is>
+      </c>
+      <c r="B76" s="10">
+        <f>MAX(1,CEILING($B$74/($B$75*$B$17),1))</f>
         <v/>
       </c>
       <c r="C76" s="5" t="inlineStr"/>
@@ -3675,18 +3687,14 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Lp (µH)（反激）</t>
-        </is>
-      </c>
-      <c r="B77" s="12">
-        <f>IF($B$52,1000000*($B$9*$B$63/($B$19*$B$76*$B$41)),0)</f>
-        <v/>
-      </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>按纹波比反算</t>
-        </is>
-      </c>
+          <t>原边峰值 Ipk (A)</t>
+        </is>
+      </c>
+      <c r="B77" s="16">
+        <f>IF($B$52,IF($B$19&gt;=2,2*$B$66/($B$9*$B$64),($B$66/$B$9/$B$64)/(1-$B$19/2)),IF($B$57,$B$66/(0.5*$B$68)*1.414,($B$12+$B$20/2)/$B$69))</f>
+        <v/>
+      </c>
+      <c r="C77" s="5" t="inlineStr"/>
       <c r="D77" s="8" t="inlineStr">
         <is>
           <t>B77</t>
@@ -3696,14 +3704,18 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>ΔI_pri (A)（反激）</t>
-        </is>
-      </c>
-      <c r="B78" s="16">
-        <f>IF($B$52,$B$19*$B$76,0)</f>
-        <v/>
-      </c>
-      <c r="C78" s="5" t="inlineStr"/>
+          <t>Lp (µH)（反激）</t>
+        </is>
+      </c>
+      <c r="B78" s="12">
+        <f>IF($B$52,1000000*($B$9*$B$64/($B$19*$B$77*$B$41)),0)</f>
+        <v/>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>按纹波比反算</t>
+        </is>
+      </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
           <t>B78</t>
@@ -3713,11 +3725,11 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>谷值 (A)（反激）</t>
+          <t>ΔI_pri (A)（反激）</t>
         </is>
       </c>
       <c r="B79" s="16">
-        <f>IF($B$52,MAX($B$76-$B$78,0),0)</f>
+        <f>IF($B$52,$B$19*$B$77,0)</f>
         <v/>
       </c>
       <c r="C79" s="5" t="inlineStr"/>
@@ -3730,11 +3742,11 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>ΔI_pri@实际占空比 (A)</t>
+          <t>谷值 (A)（反激）</t>
         </is>
       </c>
       <c r="B80" s="16">
-        <f>IF($B$52,$B$9*$B$88/(($B$77/1000000)*$B$41),0)</f>
+        <f>IF($B$52,MAX($B$77-$B$79,0),0)</f>
         <v/>
       </c>
       <c r="C80" s="5" t="inlineStr"/>
@@ -3747,18 +3759,14 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>Ipk@实际占空比 (A)</t>
+          <t>ΔI_pri@实际占空比 (A)</t>
         </is>
       </c>
       <c r="B81" s="16">
-        <f>IF($B$52,$B$65/($B$9*$B$88)+$B$80/2,$B$76)</f>
-        <v/>
-      </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>与引擎同一约定</t>
-        </is>
-      </c>
+        <f>IF($B$52,$B$9*$B$89/(($B$78/1000000)*$B$41),0)</f>
+        <v/>
+      </c>
+      <c r="C81" s="5" t="inlineStr"/>
       <c r="D81" s="8" t="inlineStr">
         <is>
           <t>B81</t>
@@ -3768,14 +3776,18 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>谷值@实际占空比 (A)</t>
+          <t>Ipk@实际占空比 (A)</t>
         </is>
       </c>
       <c r="B82" s="16">
-        <f>IF($B$52,$B$65/($B$9*$B$88)-$B$80/2,0)</f>
-        <v/>
-      </c>
-      <c r="C82" s="5" t="inlineStr"/>
+        <f>IF($B$52,$B$66/($B$9*$B$89)+$B$81/2,$B$77)</f>
+        <v/>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>与引擎同一约定</t>
+        </is>
+      </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
           <t>B82</t>
@@ -3785,11 +3797,11 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>不饱和决定 Np 下限</t>
-        </is>
-      </c>
-      <c r="B83" s="10">
-        <f>IF($B$52,CEILING(($B$77/1000000)*$B$76/($B$74*$B$48*$B$18),1),0)</f>
+          <t>谷值@实际占空比 (A)</t>
+        </is>
+      </c>
+      <c r="B83" s="16">
+        <f>IF($B$52,$B$66/($B$9*$B$89)-$B$81/2,0)</f>
         <v/>
       </c>
       <c r="C83" s="5" t="inlineStr"/>
@@ -3802,18 +3814,14 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>Np (匝)</t>
+          <t>不饱和决定 Np 下限</t>
         </is>
       </c>
       <c r="B84" s="10">
-        <f>MAX(1,$B$75,$B$83)</f>
-        <v/>
-      </c>
-      <c r="C84" s="5" t="inlineStr">
-        <is>
-          <t>磁通与不饱和下限取大者</t>
-        </is>
-      </c>
+        <f>IF($B$52,CEILING(($B$78/1000000)*$B$77/($B$75*$B$48*$B$18),1),0)</f>
+        <v/>
+      </c>
+      <c r="C84" s="5" t="inlineStr"/>
       <c r="D84" s="8" t="inlineStr">
         <is>
           <t>B84</t>
@@ -3823,14 +3831,18 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>Ns 自动取整</t>
+          <t>Np (匝)</t>
         </is>
       </c>
       <c r="B85" s="10">
-        <f>MAX(1,ROUND($B$84/$B$68,0))</f>
-        <v/>
-      </c>
-      <c r="C85" s="5" t="inlineStr"/>
+        <f>MAX(1,$B$76,$B$84)</f>
+        <v/>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>磁通与不饱和下限取大者</t>
+        </is>
+      </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
           <t>B85</t>
@@ -3840,18 +3852,14 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>Ns (匝)</t>
+          <t>Ns 自动取整</t>
         </is>
       </c>
       <c r="B86" s="10">
-        <f>IF($B$8&gt;0,$B$8,$B$85)</f>
-        <v/>
-      </c>
-      <c r="C86" s="5" t="inlineStr">
-        <is>
-          <t>可手动覆盖（评审供应商方案）</t>
-        </is>
-      </c>
+        <f>MAX(1,ROUND($B$85/$B$69,0))</f>
+        <v/>
+      </c>
+      <c r="C86" s="5" t="inlineStr"/>
       <c r="D86" s="8" t="inlineStr">
         <is>
           <t>B86</t>
@@ -3861,14 +3869,18 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>实际变比 n=Np/Ns</t>
-        </is>
-      </c>
-      <c r="B87" s="14">
-        <f>$B$84/$B$86</f>
-        <v/>
-      </c>
-      <c r="C87" s="5" t="inlineStr"/>
+          <t>Ns (匝)</t>
+        </is>
+      </c>
+      <c r="B87" s="10">
+        <f>IF($B$8&gt;0,$B$8,$B$86)</f>
+        <v/>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>可手动覆盖（评审供应商方案）</t>
+        </is>
+      </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
           <t>B87</t>
@@ -3878,11 +3890,11 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>D@Vin_min（实际比）</t>
+          <t>实际变比 n=Np/Ns</t>
         </is>
       </c>
       <c r="B88" s="14">
-        <f>IF($B$52,$B$87*$B$66/($B$9+$B$87*$B$66),IF($B$53,$B$87*$B$66/$B$9,IF($B$58,$B$87*$B$66/($B$60*$B$9),0.5)))</f>
+        <f>$B$85/$B$87</f>
         <v/>
       </c>
       <c r="C88" s="5" t="inlineStr"/>
@@ -3895,11 +3907,11 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>D@Vin_max（实际比）</t>
+          <t>D@Vin_min（实际比）</t>
         </is>
       </c>
       <c r="B89" s="14">
-        <f>IF($B$52,$B$87*$B$66/($B$10+$B$87*$B$66),IF($B$53,$B$87*$B$66/$B$10,IF($B$58,$B$87*$B$66/($B$60*$B$10),0.5)))</f>
+        <f>IF($B$52,$B$88*$B$67/($B$9+$B$88*$B$67),IF($B$53,$B$88*$B$67/$B$9,IF($B$58,$B$88*$B$67/($B$60*$B$9),0.5)))</f>
         <v/>
       </c>
       <c r="C89" s="5" t="inlineStr"/>
@@ -3912,11 +3924,11 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>V·t（实际比，Vin_min 端）</t>
-        </is>
-      </c>
-      <c r="B90" s="15">
-        <f>$B$61*$B$9*$B$88/$B$41</f>
+          <t>D@Vin_max（实际比）</t>
+        </is>
+      </c>
+      <c r="B90" s="14">
+        <f>IF($B$52,$B$88*$B$67/($B$10+$B$88*$B$67),IF($B$53,$B$88*$B$67/$B$10,IF($B$58,$B$88*$B$67/($B$60*$B$10),0.5)))</f>
         <v/>
       </c>
       <c r="C90" s="5" t="inlineStr"/>
@@ -3929,11 +3941,11 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>V·t（实际比，Vin_max 端）</t>
+          <t>V·t（实际比，Vin_min 端）</t>
         </is>
       </c>
       <c r="B91" s="15">
-        <f>$B$61*$B$10*$B$89/$B$41</f>
+        <f>$B$61*$B$9*$B$89/$B$41</f>
         <v/>
       </c>
       <c r="C91" s="5" t="inlineStr"/>
@@ -3946,18 +3958,14 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>ΔB_pp (T)</t>
-        </is>
-      </c>
-      <c r="B92" s="14">
-        <f>MAX($B$90,$B$91)/($B$84*$B$74)</f>
-        <v/>
-      </c>
-      <c r="C92" s="5" t="inlineStr">
-        <is>
-          <t>取两端较恶劣者（反激摆动最大在 Vin_max）</t>
-        </is>
-      </c>
+          <t>V·t（实际比，Vin_max 端）</t>
+        </is>
+      </c>
+      <c r="B92" s="15">
+        <f>$B$61*$B$10*$B$90/$B$41</f>
+        <v/>
+      </c>
+      <c r="C92" s="5" t="inlineStr"/>
       <c r="D92" s="8" t="inlineStr">
         <is>
           <t>B92</t>
@@ -3967,14 +3975,18 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>允许峰值 Bsat·降额 (T)</t>
-        </is>
-      </c>
-      <c r="B93" s="16">
-        <f>$B$48*$B$18</f>
-        <v/>
-      </c>
-      <c r="C93" s="5" t="inlineStr"/>
+          <t>ΔB_pp (T)</t>
+        </is>
+      </c>
+      <c r="B93" s="14">
+        <f>MAX($B$91,$B$92)/($B$85*$B$75)</f>
+        <v/>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>取两端较恶劣者（反激摆动最大在 Vin_max）</t>
+        </is>
+      </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
           <t>B93</t>
@@ -3984,18 +3996,14 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>AL (nH/N²)</t>
-        </is>
-      </c>
-      <c r="B94" s="10">
-        <f>IF($B$46&gt;0,$B$46,1000000*4*PI()*0.0000001*$B$47*$B$74/($B$43/1000))</f>
-        <v/>
-      </c>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
-          <t>实测优先，否则 µ0·µi·Ae/le</t>
-        </is>
-      </c>
+          <t>允许峰值 Bsat·降额 (T)</t>
+        </is>
+      </c>
+      <c r="B94" s="16">
+        <f>$B$48*$B$18</f>
+        <v/>
+      </c>
+      <c r="C94" s="5" t="inlineStr"/>
       <c r="D94" s="8" t="inlineStr">
         <is>
           <t>B94</t>
@@ -4005,14 +4013,18 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>Lm (µH) = AL·Np²</t>
-        </is>
-      </c>
-      <c r="B95" s="12">
-        <f>$B$94/1000000000*$B$84*$B$84*1000000</f>
-        <v/>
-      </c>
-      <c r="C95" s="5" t="inlineStr"/>
+          <t>AL (nH/N²)</t>
+        </is>
+      </c>
+      <c r="B95" s="10">
+        <f>IF($B$46&gt;0,$B$46,1000000*4*PI()*0.0000001*$B$47*$B$75/($B$43/1000))</f>
+        <v/>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>实测优先，否则 µ0·µi·Ae/le</t>
+        </is>
+      </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
           <t>B95</t>
@@ -4022,11 +4034,11 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>ΔI_m (A) = V·t/Lm</t>
-        </is>
-      </c>
-      <c r="B96" s="14">
-        <f>$B$73/($B$95/1000000)</f>
+          <t>Lm (µH) = AL·Np²</t>
+        </is>
+      </c>
+      <c r="B96" s="12">
+        <f>$B$95/1000000000*$B$85*$B$85*1000000</f>
         <v/>
       </c>
       <c r="C96" s="5" t="inlineStr"/>
@@ -4039,18 +4051,14 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>Bpk (T)</t>
+          <t>ΔI_m (A) = V·t/Lm</t>
         </is>
       </c>
       <c r="B97" s="14">
-        <f>IF($B$52,$B$77/1000000*$B$81/($B$84*$B$74),IF(OR($B$58,$B$57),$B$92/2,$B$92))</f>
-        <v/>
-      </c>
-      <c r="C97" s="5" t="inlineStr">
-        <is>
-          <t>单极性 Bpk=ΔB；双极性减半；反激 Lp·Ipk/(Np·Ae)</t>
-        </is>
-      </c>
+        <f>$B$74/($B$96/1000000)</f>
+        <v/>
+      </c>
+      <c r="C97" s="5" t="inlineStr"/>
       <c r="D97" s="8" t="inlineStr">
         <is>
           <t>B97</t>
@@ -4060,14 +4068,18 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>原边峰值(含励磁) (A)</t>
-        </is>
-      </c>
-      <c r="B98" s="16">
-        <f>IF($B$52,$B$76,$B$76+$B$96/2)</f>
-        <v/>
-      </c>
-      <c r="C98" s="5" t="inlineStr"/>
+          <t>Bpk (T)</t>
+        </is>
+      </c>
+      <c r="B98" s="14">
+        <f>IF($B$52,$B$78/1000000*$B$82/($B$85*$B$75),IF(OR($B$58,$B$57),$B$93/2,$B$93))</f>
+        <v/>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>单极性 Bpk=ΔB；双极性减半；反激 Lp·Ipk/(Np·Ae)</t>
+        </is>
+      </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
           <t>B98</t>
@@ -4077,11 +4089,11 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>副边电流下沿 (A)</t>
+          <t>原边峰值(含励磁) (A)</t>
         </is>
       </c>
       <c r="B99" s="16">
-        <f>$B$12-$B$20/2</f>
+        <f>IF($B$52,$B$77,$B$77+$B$97/2)</f>
         <v/>
       </c>
       <c r="C99" s="5" t="inlineStr"/>
@@ -4094,11 +4106,11 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>副边电流上沿 (A)</t>
+          <t>副边电流下沿 (A)</t>
         </is>
       </c>
       <c r="B100" s="16">
-        <f>$B$12+$B$20/2</f>
+        <f>$B$12-$B$20/2</f>
         <v/>
       </c>
       <c r="C100" s="5" t="inlineStr"/>
@@ -4111,11 +4123,11 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>原边电流下沿 (A)</t>
+          <t>副边电流上沿 (A)</t>
         </is>
       </c>
       <c r="B101" s="16">
-        <f>IF($B$52,0,$B$99/$B$87)</f>
+        <f>$B$12+$B$20/2</f>
         <v/>
       </c>
       <c r="C101" s="5" t="inlineStr"/>
@@ -4128,11 +4140,11 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>原边电流上沿 (A)</t>
+          <t>原边电流下沿 (A)</t>
         </is>
       </c>
       <c r="B102" s="16">
-        <f>IF($B$52,0,$B$100/$B$87)</f>
+        <f>IF($B$52,0,$B$100/$B$88)</f>
         <v/>
       </c>
       <c r="C102" s="5" t="inlineStr"/>
@@ -4145,18 +4157,14 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>推挽半绕组电流倍数</t>
-        </is>
-      </c>
-      <c r="B103" s="10">
-        <f>IF($B$54,2,1)</f>
-        <v/>
-      </c>
-      <c r="C103" s="5" t="inlineStr">
-        <is>
-          <t>推挽每个半绕组电流为 2·Iout/n</t>
-        </is>
-      </c>
+          <t>原边电流上沿 (A)</t>
+        </is>
+      </c>
+      <c r="B103" s="16">
+        <f>IF($B$52,0,$B$101/$B$88)</f>
+        <v/>
+      </c>
+      <c r="C103" s="5" t="inlineStr"/>
       <c r="D103" s="8" t="inlineStr">
         <is>
           <t>B103</t>
@@ -4166,14 +4174,18 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>原边绕组下沿 (A)</t>
-        </is>
-      </c>
-      <c r="B104" s="16">
-        <f>$B$103*$B$101</f>
-        <v/>
-      </c>
-      <c r="C104" s="5" t="inlineStr"/>
+          <t>推挽半绕组电流倍数</t>
+        </is>
+      </c>
+      <c r="B104" s="10">
+        <f>IF($B$54,2,1)</f>
+        <v/>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>推挽每个半绕组电流为 2·Iout/n</t>
+        </is>
+      </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
           <t>B104</t>
@@ -4183,11 +4195,11 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>原边绕组上沿 (A)</t>
+          <t>原边绕组下沿 (A)</t>
         </is>
       </c>
       <c r="B105" s="16">
-        <f>$B$103*$B$102</f>
+        <f>$B$104*$B$102</f>
         <v/>
       </c>
       <c r="C105" s="5" t="inlineStr"/>
@@ -4200,18 +4212,14 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>桥式原边导通占比</t>
-        </is>
-      </c>
-      <c r="B106" s="14">
-        <f>IF($B$54,$B$88,2*$B$88)</f>
-        <v/>
-      </c>
-      <c r="C106" s="5" t="inlineStr">
-        <is>
-          <t>推挽每半绕组一周期导通一次</t>
-        </is>
-      </c>
+          <t>原边绕组上沿 (A)</t>
+        </is>
+      </c>
+      <c r="B106" s="16">
+        <f>$B$104*$B$103</f>
+        <v/>
+      </c>
+      <c r="C106" s="5" t="inlineStr"/>
       <c r="D106" s="8" t="inlineStr">
         <is>
           <t>B106</t>
@@ -4221,14 +4229,18 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>副边导通占比</t>
+          <t>桥式原边导通占比</t>
         </is>
       </c>
       <c r="B107" s="14">
-        <f>IF($B$58,IF($B$6="ct",$B$88,2*$B$88),$B$88)</f>
-        <v/>
-      </c>
-      <c r="C107" s="5" t="inlineStr"/>
+        <f>IF($B$54,$B$89,2*$B$89)</f>
+        <v/>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>推挽每半绕组一周期导通一次</t>
+        </is>
+      </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
           <t>B107</t>
@@ -4238,11 +4250,11 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>原边 I_rms (A)</t>
-        </is>
-      </c>
-      <c r="B108" s="16">
-        <f>IF($B$52,SQRT($B$88*($B$81^2+$B$81*$B$82+$B$82^2)/3),IF($B$53,SQRT($B$88*($B$101^2+$B$101*$B$102+$B$102^2)/3+$B$88*$B$96^2/12),IF($B$58,SQRT($B$106*($B$104^2+$B$104*$B$105+$B$105^2)/3+$B$96^2*$B$106/12),$B$65/(0.5*$B$67))))</f>
+          <t>副边导通占比</t>
+        </is>
+      </c>
+      <c r="B108" s="14">
+        <f>IF($B$58,IF($B$6="ct",$B$89,2*$B$89),$B$89)</f>
         <v/>
       </c>
       <c r="C108" s="5" t="inlineStr"/>
@@ -4255,11 +4267,11 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>副边峰值 Is_pk (A)</t>
+          <t>原边 I_rms (A)</t>
         </is>
       </c>
       <c r="B109" s="16">
-        <f>IF($B$52,$B$87*$B$81,IF($B$57,1.5708*$B$12,$B$12+$B$20/2))</f>
+        <f>IF($B$52,SQRT($B$89*($B$82^2+$B$82*$B$83+$B$83^2)/3),IF($B$53,SQRT($B$89*($B$102^2+$B$102*$B$103+$B$103^2)/3+$B$89*$B$97^2/12),IF($B$58,SQRT($B$107*($B$105^2+$B$105*$B$106+$B$106^2)/3+$B$97^2*$B$107/12),$B$66/(0.5*$B$68))))</f>
         <v/>
       </c>
       <c r="C109" s="5" t="inlineStr"/>
@@ -4272,11 +4284,11 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>副边 I_rms (A)</t>
+          <t>副边峰值 Is_pk (A)</t>
         </is>
       </c>
       <c r="B110" s="16">
-        <f>IF($B$52,$B$87*SQRT((1-$B$88)*($B$81^2+$B$81*$B$82+$B$82^2)/3),IF($B$57,1.1107*$B$12,SQRT(IF($B$59,$B$107*($B$99^2+$B$99*$B$100+$B$100^2)/3,($B$99^2+$B$99*$B$100+$B$100^2)/3))))</f>
+        <f>IF($B$52,$B$88*$B$82,IF($B$57,1.5708*$B$12,$B$12+$B$20/2))</f>
         <v/>
       </c>
       <c r="C110" s="5" t="inlineStr"/>
@@ -4289,11 +4301,11 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>副边导通期平均 (A)</t>
+          <t>副边 I_rms (A)</t>
         </is>
       </c>
       <c r="B111" s="16">
-        <f>IF($B$52,$B$65/$B$66,IF($B$53,$B$88*$B$12,$B$12))</f>
+        <f>IF($B$52,$B$88*SQRT((1-$B$89)*($B$82^2+$B$82*$B$83+$B$83^2)/3),IF($B$57,1.1107*$B$12,SQRT(IF($B$59,$B$108*($B$100^2+$B$100*$B$101+$B$101^2)/3,($B$100^2+$B$100*$B$101+$B$101^2)/3))))</f>
         <v/>
       </c>
       <c r="C111" s="5" t="inlineStr"/>
@@ -4306,11 +4318,11 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>副边绕组数</t>
-        </is>
-      </c>
-      <c r="B112" s="10">
-        <f>IF(AND($B$58,$B$6="ct"),2,1)</f>
+          <t>副边导通期平均 (A)</t>
+        </is>
+      </c>
+      <c r="B112" s="16">
+        <f>IF($B$52,$B$66/$B$67,IF($B$53,$B$89*$B$12,$B$12))</f>
         <v/>
       </c>
       <c r="C112" s="5" t="inlineStr"/>
@@ -4323,11 +4335,11 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>原边单股线径 (mm)</t>
-        </is>
-      </c>
-      <c r="B113" s="16">
-        <f>IF($B$33="auto",CEILING(SQRT(4*($B$108/$B$21)/($B$35*$B$36)/PI()),0.05),$B$34)</f>
+          <t>副边绕组数</t>
+        </is>
+      </c>
+      <c r="B113" s="10">
+        <f>IF(AND($B$58,$B$6="ct"),2,1)</f>
         <v/>
       </c>
       <c r="C113" s="5" t="inlineStr"/>
@@ -4340,11 +4352,11 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>副边单股线径 (mm)</t>
+          <t>原边单股线径 (mm)</t>
         </is>
       </c>
       <c r="B114" s="16">
-        <f>IF($B$37="auto",CEILING(SQRT(4*($B$110/$B$21)/($B$39*$B$40)/PI()),0.05),$B$38)</f>
+        <f>IF($B$33="auto",CEILING(SQRT(4*($B$109/$B$21)/($B$35*$B$36)/PI()),0.05),$B$34)</f>
         <v/>
       </c>
       <c r="C114" s="5" t="inlineStr"/>
@@ -4357,11 +4369,11 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>原边铜面积/匝 (mm²)</t>
-        </is>
-      </c>
-      <c r="B115" s="14">
-        <f>PI()/4*$B$113^2*$B$35*$B$36</f>
+          <t>副边单股线径 (mm)</t>
+        </is>
+      </c>
+      <c r="B115" s="16">
+        <f>IF($B$37="auto",CEILING(SQRT(4*($B$111/$B$21)/($B$39*$B$40)/PI()),0.05),$B$38)</f>
         <v/>
       </c>
       <c r="C115" s="5" t="inlineStr"/>
@@ -4374,11 +4386,11 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>副边铜面积/匝 (mm²)</t>
+          <t>原边铜面积/匝 (mm²)</t>
         </is>
       </c>
       <c r="B116" s="14">
-        <f>PI()/4*$B$114^2*$B$39*$B$40</f>
+        <f>PI()/4*$B$114^2*$B$35*$B$36</f>
         <v/>
       </c>
       <c r="C116" s="5" t="inlineStr"/>
@@ -4391,18 +4403,14 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>正激复位匝数 Nr</t>
-        </is>
-      </c>
-      <c r="B117" s="10">
-        <f>IF($B$53,CEILING($B$84*$B$63/(1-$B$63),1),0)</f>
-        <v/>
-      </c>
-      <c r="C117" s="5" t="inlineStr">
-        <is>
-          <t>Nr/Np ≥ D/(1-D)</t>
-        </is>
-      </c>
+          <t>副边铜面积/匝 (mm²)</t>
+        </is>
+      </c>
+      <c r="B117" s="14">
+        <f>PI()/4*$B$115^2*$B$39*$B$40</f>
+        <v/>
+      </c>
+      <c r="C117" s="5" t="inlineStr"/>
       <c r="D117" s="8" t="inlineStr">
         <is>
           <t>B117</t>
@@ -4412,14 +4420,18 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>总铜面积 (mm²)</t>
-        </is>
-      </c>
-      <c r="B118" s="16">
-        <f>$B$84*$B$115+$B$86*$B$116*$B$112+$B$117*$B$115</f>
-        <v/>
-      </c>
-      <c r="C118" s="5" t="inlineStr"/>
+          <t>正激复位匝数 Nr</t>
+        </is>
+      </c>
+      <c r="B118" s="10">
+        <f>IF($B$53,CEILING($B$85*$B$64/(1-$B$64),1),0)</f>
+        <v/>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>Nr/Np ≥ D/(1-D)</t>
+        </is>
+      </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
           <t>B118</t>
@@ -4429,18 +4441,14 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>窗口填充率 (%)</t>
-        </is>
-      </c>
-      <c r="B119" s="12">
-        <f>$B$118*$B$23/$B$44*100</f>
-        <v/>
-      </c>
-      <c r="C119" s="5" t="inlineStr">
-        <is>
-          <t>与 Ku 比较</t>
-        </is>
-      </c>
+          <t>总铜面积 (mm²)</t>
+        </is>
+      </c>
+      <c r="B119" s="16">
+        <f>$B$85*$B$116+$B$87*$B$117*$B$113+$B$118*$B$116</f>
+        <v/>
+      </c>
+      <c r="C119" s="5" t="inlineStr"/>
       <c r="D119" s="8" t="inlineStr">
         <is>
           <t>B119</t>
@@ -4450,14 +4458,18 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>满足 Ku 所需 Aw (mm²)</t>
-        </is>
-      </c>
-      <c r="B120" s="11">
-        <f>$B$118*$B$23/$B$22</f>
-        <v/>
-      </c>
-      <c r="C120" s="5" t="inlineStr"/>
+          <t>窗口填充率 (%)</t>
+        </is>
+      </c>
+      <c r="B120" s="12">
+        <f>$B$119*$B$23/$B$44*100</f>
+        <v/>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>与 Ku 比较</t>
+        </is>
+      </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
           <t>B120</t>
@@ -4467,11 +4479,11 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>原边电流密度 (A/mm²)</t>
-        </is>
-      </c>
-      <c r="B121" s="12">
-        <f>$B$108/$B$115</f>
+          <t>满足 Ku 所需 Aw (mm²)</t>
+        </is>
+      </c>
+      <c r="B121" s="11">
+        <f>$B$119*$B$23/$B$22</f>
         <v/>
       </c>
       <c r="C121" s="5" t="inlineStr"/>
@@ -4484,11 +4496,11 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>副边电流密度 (A/mm²)</t>
+          <t>原边电流密度 (A/mm²)</t>
         </is>
       </c>
       <c r="B122" s="12">
-        <f>$B$110/$B$116</f>
+        <f>$B$109/$B$116</f>
         <v/>
       </c>
       <c r="C122" s="5" t="inlineStr"/>
@@ -4501,11 +4513,11 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>原边 DCR@25°C (mΩ)</t>
+          <t>副边电流密度 (A/mm²)</t>
         </is>
       </c>
       <c r="B123" s="12">
-        <f>1000*1.758e-08*($B$45/1000)*$B$84/($B$115/1000000)</f>
+        <f>$B$111/$B$117</f>
         <v/>
       </c>
       <c r="C123" s="5" t="inlineStr"/>
@@ -4518,11 +4530,11 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>副边 DCR@25°C (mΩ)</t>
+          <t>原边 DCR@25°C (mΩ)</t>
         </is>
       </c>
       <c r="B124" s="12">
-        <f>1000*1.758e-08*($B$45/1000)*$B$86/($B$116/1000000)</f>
+        <f>1000*1.758e-08*($B$45/1000)*$B$85/($B$116/1000000)</f>
         <v/>
       </c>
       <c r="C124" s="5" t="inlineStr"/>
@@ -4535,11 +4547,11 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>原边铜损 (W)</t>
-        </is>
-      </c>
-      <c r="B125" s="16">
-        <f>$B$108^2*2.266e-08*($B$45/1000)*$B$84/($B$115/1000000)*$B$27</f>
+          <t>副边 DCR@25°C (mΩ)</t>
+        </is>
+      </c>
+      <c r="B125" s="12">
+        <f>1000*1.758e-08*($B$45/1000)*$B$87/($B$117/1000000)</f>
         <v/>
       </c>
       <c r="C125" s="5" t="inlineStr"/>
@@ -4552,11 +4564,11 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>副边铜损 (W)</t>
+          <t>原边铜损 (W)</t>
         </is>
       </c>
       <c r="B126" s="16">
-        <f>$B$110^2*2.266e-08*($B$45/1000)*$B$86/($B$116/1000000)*$B$27*$B$112</f>
+        <f>$B$109^2*2.266e-08*($B$45/1000)*$B$85/($B$116/1000000)*$B$27</f>
         <v/>
       </c>
       <c r="C126" s="5" t="inlineStr"/>
@@ -4569,11 +4581,11 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>总铜损@100°C 初值 (W)</t>
+          <t>副边铜损 (W)</t>
         </is>
       </c>
       <c r="B127" s="16">
-        <f>$B$125+$B$126</f>
+        <f>$B$111^2*2.266e-08*($B$45/1000)*$B$87/($B$117/1000000)*$B$27*$B$113</f>
         <v/>
       </c>
       <c r="C127" s="5" t="inlineStr"/>
@@ -4586,11 +4598,11 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>铜电阻率@20°C (Ω·m)</t>
-        </is>
-      </c>
-      <c r="B128" s="15">
-        <f>0.00000001724</f>
+          <t>总铜损@100°C 初值 (W)</t>
+        </is>
+      </c>
+      <c r="B128" s="16">
+        <f>$B$126+$B$127</f>
         <v/>
       </c>
       <c r="C128" s="5" t="inlineStr"/>
@@ -4603,18 +4615,14 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>温升初值 (K)</t>
-        </is>
-      </c>
-      <c r="B129" s="12">
-        <f>($B$127+$B$137)*$B$24</f>
-        <v/>
-      </c>
-      <c r="C129" s="5" t="inlineStr">
-        <is>
-          <t>用 100°C 初值先估一次</t>
-        </is>
-      </c>
+          <t>铜电阻率@20°C (Ω·m)</t>
+        </is>
+      </c>
+      <c r="B129" s="15">
+        <f>0.00000001724</f>
+        <v/>
+      </c>
+      <c r="C129" s="5" t="inlineStr"/>
       <c r="D129" s="8" t="inlineStr">
         <is>
           <t>B129</t>
@@ -4624,14 +4632,18 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>绕组温度估计 (°C)</t>
-        </is>
-      </c>
-      <c r="B130" s="11">
-        <f>$B$26+$B$129</f>
-        <v/>
-      </c>
-      <c r="C130" s="5" t="inlineStr"/>
+          <t>温升初值 (K)</t>
+        </is>
+      </c>
+      <c r="B130" s="12">
+        <f>($B$128+$B$138)*$B$24</f>
+        <v/>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>用 100°C 初值先估一次</t>
+        </is>
+      </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
           <t>B130</t>
@@ -4641,11 +4653,11 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>铜电阻率@绕组温度 (Ω·m)</t>
-        </is>
-      </c>
-      <c r="B131" s="15">
-        <f>$B$128*(1+0.00393*($B$130-20))</f>
+          <t>绕组温度估计 (°C)</t>
+        </is>
+      </c>
+      <c r="B131" s="11">
+        <f>$B$26+$B$130</f>
         <v/>
       </c>
       <c r="C131" s="5" t="inlineStr"/>
@@ -4658,11 +4670,11 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>原边铜损（迭代）(W)</t>
-        </is>
-      </c>
-      <c r="B132" s="16">
-        <f>$B$108^2*$B$131*($B$45/1000)*$B$84/($B$115/1000000)*$B$27</f>
+          <t>铜电阻率@绕组温度 (Ω·m)</t>
+        </is>
+      </c>
+      <c r="B132" s="15">
+        <f>$B$129*(1+0.00393*($B$131-20))</f>
         <v/>
       </c>
       <c r="C132" s="5" t="inlineStr"/>
@@ -4675,11 +4687,11 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>副边铜损（迭代）(W)</t>
+          <t>原边铜损（迭代）(W)</t>
         </is>
       </c>
       <c r="B133" s="16">
-        <f>$B$110^2*$B$131*($B$45/1000)*$B$86/($B$116/1000000)*$B$27*$B$112</f>
+        <f>$B$109^2*$B$132*($B$45/1000)*$B$85/($B$116/1000000)*$B$27</f>
         <v/>
       </c>
       <c r="C133" s="5" t="inlineStr"/>
@@ -4692,18 +4704,14 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>总铜损（一次温度迭代）(W)</t>
+          <t>副边铜损（迭代）(W)</t>
         </is>
       </c>
       <c r="B134" s="16">
-        <f>$B$132+$B$133</f>
-        <v/>
-      </c>
-      <c r="C134" s="5" t="inlineStr">
-        <is>
-          <t>引擎为收敛迭代，本表一次迭代</t>
-        </is>
-      </c>
+        <f>$B$111^2*$B$132*($B$45/1000)*$B$87/($B$117/1000000)*$B$27*$B$113</f>
+        <v/>
+      </c>
+      <c r="C134" s="5" t="inlineStr"/>
       <c r="D134" s="8" t="inlineStr">
         <is>
           <t>B134</t>
@@ -4713,14 +4721,18 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>B_ac = ΔB_pp/2 (T)</t>
-        </is>
-      </c>
-      <c r="B135" s="14">
-        <f>$B$92/2</f>
-        <v/>
-      </c>
-      <c r="C135" s="5" t="inlineStr"/>
+          <t>总铜损（一次温度迭代）(W)</t>
+        </is>
+      </c>
+      <c r="B135" s="16">
+        <f>$B$133+$B$134</f>
+        <v/>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>引擎为收敛迭代，本表一次迭代</t>
+        </is>
+      </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
           <t>B135</t>
@@ -4730,11 +4742,11 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>Pcv (kW/m³)</t>
-        </is>
-      </c>
-      <c r="B136" s="11">
-        <f>$B$49*($B$14/100)^$B$50*($B$135*1000/100)^$B$51</f>
+          <t>B_ac = ΔB_pp/2 (T)</t>
+        </is>
+      </c>
+      <c r="B136" s="14">
+        <f>$B$93/2</f>
         <v/>
       </c>
       <c r="C136" s="5" t="inlineStr"/>
@@ -4747,18 +4759,14 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>磁芯损耗 (W)</t>
-        </is>
-      </c>
-      <c r="B137" s="16">
-        <f>$B$136*($B$42*$B$43)/1000000</f>
-        <v/>
-      </c>
-      <c r="C137" s="5" t="inlineStr">
-        <is>
-          <t>Ve = Ae·le (mm³)</t>
-        </is>
-      </c>
+          <t>Pcv (kW/m³)</t>
+        </is>
+      </c>
+      <c r="B137" s="11">
+        <f>$B$49*($B$14/100)^$B$50*($B$136*1000/100)^$B$51</f>
+        <v/>
+      </c>
+      <c r="C137" s="5" t="inlineStr"/>
       <c r="D137" s="8" t="inlineStr">
         <is>
           <t>B137</t>
@@ -4768,14 +4776,18 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>总损耗 (W)</t>
+          <t>磁芯损耗 (W)</t>
         </is>
       </c>
       <c r="B138" s="16">
-        <f>$B$134+$B$137</f>
-        <v/>
-      </c>
-      <c r="C138" s="5" t="inlineStr"/>
+        <f>$B$137*($B$42*$B$43)/1000000</f>
+        <v/>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>Ve = Ae·le (mm³)</t>
+        </is>
+      </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
           <t>B138</t>
@@ -4785,11 +4797,11 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>温升 ΔT (K)</t>
-        </is>
-      </c>
-      <c r="B139" s="12">
-        <f>$B$138*$B$24</f>
+          <t>总损耗 (W)</t>
+        </is>
+      </c>
+      <c r="B139" s="16">
+        <f>$B$135+$B$138</f>
         <v/>
       </c>
       <c r="C139" s="5" t="inlineStr"/>
@@ -4802,11 +4814,11 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>满足目标温升所需 Rth (K/W)</t>
-        </is>
-      </c>
-      <c r="B140" s="11">
-        <f>$B$25/$B$138</f>
+          <t>温升 ΔT (K)</t>
+        </is>
+      </c>
+      <c r="B140" s="12">
+        <f>$B$139*$B$24</f>
         <v/>
       </c>
       <c r="C140" s="5" t="inlineStr"/>
@@ -4819,18 +4831,14 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>输出电感 L (µH)</t>
-        </is>
-      </c>
-      <c r="B141" s="12">
-        <f>IF($B$59,1000000*$B$66*(1-$B$88)/($B$20*$B$41),0)</f>
-        <v/>
-      </c>
-      <c r="C141" s="5" t="inlineStr">
-        <is>
-          <t>Vin_min 设计点</t>
-        </is>
-      </c>
+          <t>满足目标温升所需 Rth (K/W)</t>
+        </is>
+      </c>
+      <c r="B141" s="11">
+        <f>$B$25/$B$139</f>
+        <v/>
+      </c>
+      <c r="C141" s="5" t="inlineStr"/>
       <c r="D141" s="8" t="inlineStr">
         <is>
           <t>B141</t>
@@ -4840,14 +4848,18 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>ΔI_L@Vin_max (A)</t>
-        </is>
-      </c>
-      <c r="B142" s="16">
-        <f>IF($B$59,$B$20*(1-$B$89)/(1-$B$88),0)</f>
-        <v/>
-      </c>
-      <c r="C142" s="5" t="inlineStr"/>
+          <t>输出电感 L (µH)</t>
+        </is>
+      </c>
+      <c r="B142" s="12">
+        <f>IF($B$59,1000000*$B$67*(1-$B$89)/($B$20*$B$41),0)</f>
+        <v/>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>Vin_min 设计点</t>
+        </is>
+      </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
           <t>B142</t>
@@ -4857,11 +4869,11 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>输出电感峰值 (A)</t>
+          <t>ΔI_L@Vin_max (A)</t>
         </is>
       </c>
       <c r="B143" s="16">
-        <f>IF($B$59,$B$12+$B$142/2,0)</f>
+        <f>IF($B$59,$B$20*(1-$B$90)/(1-$B$89),0)</f>
         <v/>
       </c>
       <c r="C143" s="5" t="inlineStr"/>
@@ -4874,11 +4886,11 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>输出电感匝数</t>
-        </is>
-      </c>
-      <c r="B144" s="10">
-        <f>IF($B$59,CEILING($B$141/1000000*$B$143/($B$74*$B$93),1),0)</f>
+          <t>输出电感峰值 (A)</t>
+        </is>
+      </c>
+      <c r="B144" s="16">
+        <f>IF($B$59,$B$12+$B$143/2,0)</f>
         <v/>
       </c>
       <c r="C144" s="5" t="inlineStr"/>
@@ -4891,11 +4903,11 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>输出电感 AL (nH/N²)</t>
+          <t>输出电感匝数</t>
         </is>
       </c>
       <c r="B145" s="10">
-        <f>IF($B$59,($B$141/1000000)/$B$144^2*1000000000,0)</f>
+        <f>IF($B$59,CEILING($B$142/1000000*$B$144/($B$75*$B$94),1),0)</f>
         <v/>
       </c>
       <c r="C145" s="5" t="inlineStr"/>
@@ -4908,18 +4920,14 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>输出电感气隙 (mm)</t>
-        </is>
-      </c>
-      <c r="B146" s="16">
-        <f>IF($B$59,1000*(4*PI()*0.0000001*$B$74*$B$144^2/($B$141/1000000) - $B$43/1000/$B$47),0)</f>
-        <v/>
-      </c>
-      <c r="C146" s="5" t="inlineStr">
-        <is>
-          <t>AL = µ0·Ae/(lg+le/µi)，AL=L/N²</t>
-        </is>
-      </c>
+          <t>输出电感 AL (nH/N²)</t>
+        </is>
+      </c>
+      <c r="B146" s="10">
+        <f>IF($B$59,($B$142/1000000)/$B$145^2*1000000000,0)</f>
+        <v/>
+      </c>
+      <c r="C146" s="5" t="inlineStr"/>
       <c r="D146" s="8" t="inlineStr">
         <is>
           <t>B146</t>
@@ -4929,14 +4937,18 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>输出电感 Bpk (T)</t>
-        </is>
-      </c>
-      <c r="B147" s="14">
-        <f>IF($B$59,$B$141/1000000*$B$143/($B$144*$B$74),0)</f>
-        <v/>
-      </c>
-      <c r="C147" s="5" t="inlineStr"/>
+          <t>输出电感气隙 (mm)</t>
+        </is>
+      </c>
+      <c r="B147" s="16">
+        <f>IF($B$59,1000*(4*PI()*0.0000001*$B$75*$B$145^2/($B$142/1000000) - $B$43/1000/$B$47),0)</f>
+        <v/>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>AL = µ0·Ae/(lg+le/µi)，AL=L/N²</t>
+        </is>
+      </c>
       <c r="D147" s="8" t="inlineStr">
         <is>
           <t>B147</t>
@@ -4946,11 +4958,11 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>纹波预算 (V)</t>
+          <t>输出电感 Bpk (T)</t>
         </is>
       </c>
       <c r="B148" s="14">
-        <f>$B$11*$B$28/100</f>
+        <f>IF($B$59,$B$142/1000000*$B$144/($B$145*$B$75),0)</f>
         <v/>
       </c>
       <c r="C148" s="5" t="inlineStr"/>
@@ -4963,11 +4975,11 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>输出电容纹波电流 (A)</t>
-        </is>
-      </c>
-      <c r="B149" s="16">
-        <f>IF($B$59,$B$142/SQRT(12),SQRT(MAX($B$110^2-$B$12^2,0)))</f>
+          <t>纹波预算 (V)</t>
+        </is>
+      </c>
+      <c r="B149" s="14">
+        <f>$B$11*$B$28/100</f>
         <v/>
       </c>
       <c r="C149" s="5" t="inlineStr"/>
@@ -4980,11 +4992,11 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>电容纹波电流峰值 (A)</t>
+          <t>输出电容纹波电流 (A)</t>
         </is>
       </c>
       <c r="B150" s="16">
-        <f>IF($B$59,$B$142,IF($B$57,SQRT(2)*$B$149,$B$109))</f>
+        <f>IF($B$59,$B$143/SQRT(12),SQRT(MAX($B$111^2-$B$12^2,0)))</f>
         <v/>
       </c>
       <c r="C150" s="5" t="inlineStr"/>
@@ -4997,11 +5009,11 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>ESR 分量 (V)</t>
-        </is>
-      </c>
-      <c r="B151" s="14">
-        <f>$B$150*$B$29</f>
+          <t>电容纹波电流峰值 (A)</t>
+        </is>
+      </c>
+      <c r="B151" s="16">
+        <f>IF($B$59,$B$143,IF($B$57,SQRT(2)*$B$150,$B$110))</f>
         <v/>
       </c>
       <c r="C151" s="5" t="inlineStr"/>
@@ -5014,11 +5026,11 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>输出电容 C_min (µF)</t>
-        </is>
-      </c>
-      <c r="B152" s="11">
-        <f>IF($B$151&gt;=$B$148,0,IF($B$59,1000000*$B$142/(8*$B$41*($B$148-$B$151)),IF($B$57,1000000*SQRT(2)*$B$149/(2*PI()*$B$41*($B$148-$B$151)),1000000*$B$12*$B$88/($B$41*($B$148-$B$151)))))</f>
+          <t>ESR 分量 (V)</t>
+        </is>
+      </c>
+      <c r="B152" s="14">
+        <f>$B$151*$B$29</f>
         <v/>
       </c>
       <c r="C152" s="5" t="inlineStr"/>
@@ -5031,11 +5043,11 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>ESR 上限 (mΩ)</t>
+          <t>输出电容 C_min (µF)</t>
         </is>
       </c>
       <c r="B153" s="11">
-        <f>$B$148/$B$150*1000</f>
+        <f>IF($B$152&gt;=$B$149,0,IF($B$59,1000000*$B$143/(8*$B$41*($B$149-$B$152)),IF($B$57,1000000*SQRT(2)*$B$150/(2*PI()*$B$41*($B$149-$B$152)),1000000*$B$12*$B$89/($B$41*($B$149-$B$152)))))</f>
         <v/>
       </c>
       <c r="C153" s="5" t="inlineStr"/>
@@ -5048,11 +5060,11 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>二极管损耗 (W)</t>
-        </is>
-      </c>
-      <c r="B154" s="16">
-        <f>$B$13*$B$111</f>
+          <t>ESR 上限 (mΩ)</t>
+        </is>
+      </c>
+      <c r="B154" s="11">
+        <f>$B$149/$B$151*1000</f>
         <v/>
       </c>
       <c r="C154" s="5" t="inlineStr"/>
@@ -5065,11 +5077,11 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>同步整流损耗 (W)</t>
+          <t>二极管损耗 (W)</t>
         </is>
       </c>
       <c r="B155" s="16">
-        <f>$B$30/1000*$B$110^2+$B$31*$B$111*(2*$B$32/1000000000*$B$41)</f>
+        <f>$B$13*$B$112</f>
         <v/>
       </c>
       <c r="C155" s="5" t="inlineStr"/>
@@ -5082,17 +5094,34 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>SR/二极管临界电流 (A)</t>
-        </is>
-      </c>
-      <c r="B156" s="12">
-        <f>$B$13/($B$30/1000)</f>
+          <t>同步整流损耗 (W)</t>
+        </is>
+      </c>
+      <c r="B156" s="16">
+        <f>$B$30/1000*$B$111^2+$B$31*$B$112*(2*$B$32/1000000000*$B$41)</f>
         <v/>
       </c>
       <c r="C156" s="5" t="inlineStr"/>
       <c r="D156" s="8" t="inlineStr">
         <is>
           <t>B156</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>SR/二极管临界电流 (A)</t>
+        </is>
+      </c>
+      <c r="B157" s="12">
+        <f>$B$13/($B$30/1000)</f>
+        <v/>
+      </c>
+      <c r="C157" s="5" t="inlineStr"/>
+      <c r="D157" s="8" t="inlineStr">
+        <is>
+          <t>B157</t>
         </is>
       </c>
     </row>
@@ -5130,11 +5159,11 @@
         </is>
       </c>
       <c r="B3" s="16">
-        <f>Calc!$B$97</f>
+        <f>Calc!$B$98</f>
         <v/>
       </c>
       <c r="C3" s="16">
-        <f>Calc!$B$93</f>
+        <f>Calc!$B$94</f>
         <v/>
       </c>
       <c r="D3" s="3">
@@ -5149,7 +5178,7 @@
         </is>
       </c>
       <c r="B4" s="16">
-        <f>Calc!$B$88</f>
+        <f>Calc!$B$89</f>
         <v/>
       </c>
       <c r="C4" s="16">
@@ -5168,7 +5197,7 @@
         </is>
       </c>
       <c r="B5" s="16">
-        <f>Calc!$B$119</f>
+        <f>Calc!$B$120</f>
         <v/>
       </c>
       <c r="C5" s="16">
@@ -5187,7 +5216,7 @@
         </is>
       </c>
       <c r="B6" s="16">
-        <f>Calc!$B$121</f>
+        <f>Calc!$B$122</f>
         <v/>
       </c>
       <c r="C6" s="16">
@@ -5206,7 +5235,7 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>Calc!$B$122</f>
+        <f>Calc!$B$123</f>
         <v/>
       </c>
       <c r="C7" s="16">
@@ -5225,7 +5254,7 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>Calc!$B$139</f>
+        <f>Calc!$B$140</f>
         <v/>
       </c>
       <c r="C8" s="16">
@@ -5244,11 +5273,11 @@
         </is>
       </c>
       <c r="B9" s="16">
-        <f>IF(Calc!$B$53=TRUE,Calc!$B$117/Calc!$B$84,1)</f>
+        <f>IF(Calc!$B$53=TRUE,Calc!$B$118/Calc!$B$85,1)</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>IF(Calc!$B$53=TRUE,Calc!$B$63/(1-Calc!$B$63),1)</f>
+        <f>IF(Calc!$B$53=TRUE,Calc!$B$64/(1-Calc!$B$64),1)</f>
         <v/>
       </c>
       <c r="D9" s="3">
@@ -5263,11 +5292,11 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>Calc!$B$147</f>
+        <f>Calc!$B$148</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>IF(Calc!$B$59,Calc!$B$93,999)</f>
+        <f>IF(Calc!$B$59,Calc!$B$94,999)</f>
         <v/>
       </c>
       <c r="D10" s="3">
@@ -5282,7 +5311,7 @@
         </is>
       </c>
       <c r="B11" s="16">
-        <f>Calc!$B$146</f>
+        <f>Calc!$B$147</f>
         <v/>
       </c>
       <c r="C11" s="16">
@@ -5301,7 +5330,7 @@
         </is>
       </c>
       <c r="B12" s="16">
-        <f>Calc!$B$151/Calc!$B$148*100</f>
+        <f>Calc!$B$152/Calc!$B$149*100</f>
         <v/>
       </c>
       <c r="C12" s="16">
@@ -5327,7 +5356,7 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>ABS(Calc!$B$90/(Calc!$B$84*Calc!$B$74)-(Calc!$B$77/1000000)*Calc!$B$78/(Calc!$B$84*Calc!$B$74))/MAX(Calc!$B$90/(Calc!$B$84*Calc!$B$74),0.000001)</f>
+        <f>ABS(Calc!$B$91/(Calc!$B$85*Calc!$B$75)-(Calc!$B$78/1000000)*Calc!$B$79/(Calc!$B$85*Calc!$B$75))/MAX(Calc!$B$91/(Calc!$B$85*Calc!$B$75),0.000001)</f>
         <v/>
       </c>
     </row>
@@ -5338,7 +5367,7 @@
         </is>
       </c>
       <c r="B16" s="18">
-        <f>ABS(Calc!$B$94/1000000000*Calc!$B$84*Calc!$B$84-(Calc!$B$95/1000000))/(Calc!$B$95/1000000)</f>
+        <f>ABS(Calc!$B$95/1000000000*Calc!$B$85*Calc!$B$85-(Calc!$B$96/1000000))/(Calc!$B$96/1000000)</f>
         <v/>
       </c>
     </row>
@@ -5349,7 +5378,7 @@
         </is>
       </c>
       <c r="B17" s="18">
-        <f>ABS(Calc!$B$119/100*Calc!$B$44/Calc!$B$23-Calc!$B$118)/MAX(Calc!$B$118,0.000001)</f>
+        <f>ABS(Calc!$B$120/100*Calc!$B$44/Calc!$B$23-Calc!$B$119)/MAX(Calc!$B$119,0.000001)</f>
         <v/>
       </c>
     </row>
@@ -5360,7 +5389,7 @@
         </is>
       </c>
       <c r="B18" s="18">
-        <f>IF(Calc!$B$46=0,0,ABS(Calc!$B$46-1000000*4*PI()*0.0000001*Calc!$B$47*Calc!$B$74/(Calc!$B$43/1000))/(1000000*4*PI()*0.0000001*Calc!$B$47*Calc!$B$74/(Calc!$B$43/1000)))</f>
+        <f>IF(Calc!$B$46=0,0,ABS(Calc!$B$46-1000000*4*PI()*0.0000001*Calc!$B$47*Calc!$B$75/(Calc!$B$43/1000))/(1000000*4*PI()*0.0000001*Calc!$B$47*Calc!$B$75/(Calc!$B$43/1000)))</f>
         <v/>
       </c>
     </row>
